--- a/data/trans_bre/P1402-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P1402-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,17 +660,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 0,0</t>
+          <t>-1,13; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 0,85</t>
+          <t>-1,01; 0,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 0,0</t>
+          <t>-1,21; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,21</t>
+          <t>-1,06</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-88,48%</t>
+          <t>-87,23%</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,99</t>
+          <t>-0,44; 0,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 1,69</t>
+          <t>-0,95; 1,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 1,51</t>
+          <t>-0,51; 1,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,6; -0,05</t>
+          <t>-3,35; -0,09</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,12 +785,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-65,9; 365,73</t>
+          <t>-67,17; 293,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,6</t>
+          <t>-0,43</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-32,84%</t>
+          <t>-19,46%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,06; -0,09</t>
+          <t>-3,13; -0,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,51</t>
+          <t>0,17; 2,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 0,5</t>
+          <t>-2,31; 0,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 0,59</t>
+          <t>-2,03; 0,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-85,12; 7,61</t>
+          <t>-86,15; -0,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 1246,41</t>
+          <t>1,45; 1261,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-79,47; 64,86</t>
+          <t>-80,53; 46,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-74,65; 76,14</t>
+          <t>-63,21; 82,93</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,92</t>
+          <t>-3,81</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-38,53%</t>
+          <t>-54,71%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 2,17</t>
+          <t>-2,93; 2,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 1,3</t>
+          <t>-3,11; 1,27</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 0,33</t>
+          <t>-4,25; 0,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 1,7</t>
+          <t>-6,41; -1,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-49,03; 70,83</t>
+          <t>-51,28; 73,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-56,48; 47,0</t>
+          <t>-58,43; 41,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-62,85; 13,37</t>
+          <t>-63,25; 12,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-63,33; 56,02</t>
+          <t>-71,58; -29,48</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-5,06</t>
+          <t>-5,01</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-39,18%</t>
+          <t>-38,87%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 5,34</t>
+          <t>-3,16; 5,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 3,86</t>
+          <t>-4,57; 4,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 3,77</t>
+          <t>-5,0; 3,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,1; -1,77</t>
+          <t>-8,09; -2,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-27,09; 60,65</t>
+          <t>-23,54; 63,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-34,11; 41,66</t>
+          <t>-33,99; 50,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-32,45; 33,36</t>
+          <t>-33,04; 30,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-53,73; -16,09</t>
+          <t>-53,73; -18,7</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-11,75</t>
+          <t>-5,12</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-51,29%</t>
+          <t>-23,15%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 9,58</t>
+          <t>-2,95; 9,03</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-12,4; 2,06</t>
+          <t>-12,9; 1,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-11,83; 1,23</t>
+          <t>-11,6; 1,21</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-21,05; -4,62</t>
+          <t>-9,26; -0,69</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-14,09; 62,34</t>
+          <t>-12,27; 56,65</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-35,49; 8,5</t>
+          <t>-36,7; 5,54</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-37,1; 4,94</t>
+          <t>-37,61; 3,95</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-80,29; -20,36</t>
+          <t>-38,02; -4,22</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,79</t>
+          <t>-0,93</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-2,64%</t>
+          <t>-3,14%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 8,79</t>
+          <t>-5,89; 8,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 9,91</t>
+          <t>-4,68; 11,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,8; 0,78</t>
+          <t>-13,44; 1,52</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 4,7</t>
+          <t>-6,23; 3,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-23,86; 56,01</t>
+          <t>-23,89; 50,3</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-16,16; 41,2</t>
+          <t>-14,15; 47,49</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-35,88; 2,74</t>
+          <t>-35,45; 5,03</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-18,5; 18,4</t>
+          <t>-18,77; 14,29</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-1,47</t>
+          <t>-1,49</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-16,94%</t>
+          <t>-15,99%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 2,3</t>
+          <t>-0,02; 2,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 2,63</t>
+          <t>-0,2; 2,5</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 1,06</t>
+          <t>-1,69; 1,28</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 0,49</t>
+          <t>-2,73; -0,4</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 43,93</t>
+          <t>-0,66; 42,91</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 38,0</t>
+          <t>-2,31; 36,97</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-19,57; 13,26</t>
+          <t>-18,16; 16,16</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-33,61; 4,79</t>
+          <t>-26,92; -4,57</t>
         </is>
       </c>
     </row>
